--- a/excel/distribuidora-cunza-s-a_ruta_proxima_semana.xlsx
+++ b/excel/distribuidora-cunza-s-a_ruta_proxima_semana.xlsx
@@ -9863,7 +9863,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -9915,7 +9915,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -9967,7 +9967,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -10019,7 +10019,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -10071,7 +10071,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -10123,7 +10123,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -10175,7 +10175,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -10227,7 +10227,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -10279,7 +10279,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -10331,7 +10331,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -10383,7 +10383,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -10435,7 +10435,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -10487,7 +10487,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -10539,7 +10539,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -10591,7 +10591,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -10643,7 +10643,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -10747,7 +10747,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -10799,7 +10799,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -10903,7 +10903,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -10955,7 +10955,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -11007,7 +11007,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -11111,7 +11111,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -11163,7 +11163,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -11267,7 +11267,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -11319,7 +11319,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -11423,7 +11423,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -11475,7 +11475,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -11579,7 +11579,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -11631,7 +11631,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -11683,7 +11683,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -11787,7 +11787,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -11839,7 +11839,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -11891,7 +11891,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -11995,7 +11995,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -12047,7 +12047,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -12099,7 +12099,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -12203,7 +12203,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -12359,7 +12359,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -12411,7 +12411,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -12463,7 +12463,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -12515,7 +12515,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -12567,7 +12567,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -12619,7 +12619,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -12671,7 +12671,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -12723,7 +12723,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -12775,7 +12775,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -12827,7 +12827,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -12931,7 +12931,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C242" t="inlineStr">
@@ -13035,7 +13035,7 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
@@ -13087,7 +13087,7 @@
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -13139,7 +13139,7 @@
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C245" t="inlineStr">
@@ -13191,7 +13191,7 @@
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C246" t="inlineStr">
@@ -13243,7 +13243,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C247" t="inlineStr">
@@ -13295,7 +13295,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C248" t="inlineStr">
@@ -13347,7 +13347,7 @@
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C249" t="inlineStr">
@@ -13399,7 +13399,7 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -13451,7 +13451,7 @@
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C251" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C252" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C253" t="inlineStr">
@@ -13607,7 +13607,7 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
@@ -13659,7 +13659,7 @@
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C255" t="inlineStr">
@@ -13711,7 +13711,7 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
@@ -13763,7 +13763,7 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
@@ -13815,7 +13815,7 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
@@ -13867,7 +13867,7 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
@@ -13919,7 +13919,7 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
@@ -14023,7 +14023,7 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
@@ -14075,7 +14075,7 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
@@ -14127,7 +14127,7 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
@@ -14179,7 +14179,7 @@
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C265" t="inlineStr">
@@ -14231,7 +14231,7 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
@@ -14283,7 +14283,7 @@
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C267" t="inlineStr">
@@ -14335,7 +14335,7 @@
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C268" t="inlineStr">
@@ -14387,7 +14387,7 @@
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C269" t="inlineStr">
@@ -14439,7 +14439,7 @@
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C270" t="inlineStr">
@@ -14491,7 +14491,7 @@
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C271" t="inlineStr">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C272" t="inlineStr">
@@ -14595,7 +14595,7 @@
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C273" t="inlineStr">
@@ -14647,7 +14647,7 @@
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C274" t="inlineStr">
@@ -14699,7 +14699,7 @@
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C275" t="inlineStr">
@@ -14751,7 +14751,7 @@
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C276" t="inlineStr">
@@ -14803,7 +14803,7 @@
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C277" t="inlineStr">
@@ -14855,7 +14855,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C279" t="inlineStr">
@@ -14959,7 +14959,7 @@
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C280" t="inlineStr">
@@ -15011,7 +15011,7 @@
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C281" t="inlineStr">
@@ -15063,7 +15063,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -15115,7 +15115,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C284" t="inlineStr">
@@ -15219,7 +15219,7 @@
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C285" t="inlineStr">
@@ -15271,7 +15271,7 @@
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C286" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C287" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C288" t="inlineStr">
@@ -15427,7 +15427,7 @@
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C289" t="inlineStr">
@@ -15479,7 +15479,7 @@
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C290" t="inlineStr">
@@ -15531,7 +15531,7 @@
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C291" t="inlineStr">
@@ -15583,7 +15583,7 @@
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
@@ -15635,7 +15635,7 @@
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
@@ -15687,7 +15687,7 @@
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
@@ -15739,7 +15739,7 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
@@ -15791,7 +15791,7 @@
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
@@ -15843,7 +15843,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -15895,7 +15895,7 @@
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
@@ -15947,7 +15947,7 @@
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
@@ -15999,7 +15999,7 @@
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
@@ -16051,7 +16051,7 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C302" t="inlineStr">
@@ -16155,7 +16155,7 @@
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C303" t="inlineStr">
@@ -16207,7 +16207,7 @@
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C304" t="inlineStr">
@@ -16259,7 +16259,7 @@
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C305" t="inlineStr">
@@ -16311,7 +16311,7 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
@@ -16363,7 +16363,7 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
@@ -16415,7 +16415,7 @@
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C308" t="inlineStr">
@@ -16467,7 +16467,7 @@
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C309" t="inlineStr">
@@ -16519,7 +16519,7 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
@@ -16571,7 +16571,7 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
@@ -16623,7 +16623,7 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
@@ -16675,7 +16675,7 @@
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
@@ -16727,7 +16727,7 @@
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
@@ -16779,7 +16779,7 @@
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C315" t="inlineStr">
@@ -16831,7 +16831,7 @@
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C316" t="inlineStr">
@@ -16883,7 +16883,7 @@
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
@@ -16935,7 +16935,7 @@
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
@@ -16987,7 +16987,7 @@
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C319" t="inlineStr">
@@ -17039,7 +17039,7 @@
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C320" t="inlineStr">
@@ -17091,7 +17091,7 @@
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C321" t="inlineStr">
@@ -17143,7 +17143,7 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
@@ -17247,7 +17247,7 @@
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C324" t="inlineStr">
@@ -17299,7 +17299,7 @@
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C325" t="inlineStr">
@@ -17351,7 +17351,7 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
@@ -17403,7 +17403,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
@@ -17455,7 +17455,7 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
@@ -17507,7 +17507,7 @@
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C329" t="inlineStr">
@@ -17559,7 +17559,7 @@
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C330" t="inlineStr">
@@ -17611,7 +17611,7 @@
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C331" t="inlineStr">
@@ -17663,7 +17663,7 @@
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C332" t="inlineStr">
@@ -17715,7 +17715,7 @@
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
@@ -17819,7 +17819,7 @@
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C335" t="inlineStr">
@@ -17871,7 +17871,7 @@
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C336" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
@@ -17975,7 +17975,7 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
@@ -18027,7 +18027,7 @@
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C339" t="inlineStr">
@@ -18079,7 +18079,7 @@
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C340" t="inlineStr">
@@ -18131,7 +18131,7 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
@@ -18183,7 +18183,7 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
@@ -18235,7 +18235,7 @@
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
@@ -18287,7 +18287,7 @@
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
@@ -18339,7 +18339,7 @@
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C345" t="inlineStr">
@@ -18391,7 +18391,7 @@
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C346" t="inlineStr">
@@ -18443,7 +18443,7 @@
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C347" t="inlineStr">
@@ -18495,7 +18495,7 @@
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C348" t="inlineStr">
@@ -18547,7 +18547,7 @@
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C349" t="inlineStr">
@@ -18599,7 +18599,7 @@
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C350" t="inlineStr">
@@ -18651,7 +18651,7 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
@@ -18703,7 +18703,7 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
@@ -18755,7 +18755,7 @@
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C353" t="inlineStr">
@@ -18807,7 +18807,7 @@
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C354" t="inlineStr">
@@ -18859,7 +18859,7 @@
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
@@ -18911,7 +18911,7 @@
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
@@ -18963,7 +18963,7 @@
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C357" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C358" t="inlineStr">
@@ -19067,7 +19067,7 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
@@ -19119,7 +19119,7 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
@@ -19171,7 +19171,7 @@
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
+          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
         </is>
       </c>
       <c r="C361" t="inlineStr">
@@ -19223,7 +19223,7 @@
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C362" t="inlineStr">
@@ -19275,7 +19275,7 @@
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C363" t="inlineStr">
@@ -19327,7 +19327,7 @@
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
@@ -19379,7 +19379,7 @@
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
@@ -19431,7 +19431,7 @@
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C366" t="inlineStr">
@@ -19483,7 +19483,7 @@
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C367" t="inlineStr">
@@ -19535,7 +19535,7 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
@@ -19587,7 +19587,7 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
@@ -19639,7 +19639,7 @@
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C370" t="inlineStr">
@@ -19691,7 +19691,7 @@
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C371" t="inlineStr">
@@ -19743,7 +19743,7 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
@@ -19795,7 +19795,7 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
@@ -19847,7 +19847,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C374" t="inlineStr">
@@ -19899,7 +19899,7 @@
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C375" t="inlineStr">
@@ -19951,7 +19951,7 @@
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C376" t="inlineStr">
@@ -20003,7 +20003,7 @@
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C377" t="inlineStr">
@@ -20055,7 +20055,7 @@
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
@@ -20107,7 +20107,7 @@
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
@@ -20159,7 +20159,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C380" t="inlineStr">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C381" t="inlineStr">
@@ -20263,7 +20263,7 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
@@ -20315,7 +20315,7 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
@@ -20367,7 +20367,7 @@
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C384" t="inlineStr">
@@ -20419,7 +20419,7 @@
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C385" t="inlineStr">
@@ -20471,7 +20471,7 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
@@ -20523,7 +20523,7 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
@@ -20575,7 +20575,7 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
@@ -20627,7 +20627,7 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
@@ -20679,7 +20679,7 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
@@ -20731,7 +20731,7 @@
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C391" t="inlineStr">
@@ -20783,7 +20783,7 @@
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C392" t="inlineStr">
@@ -20835,7 +20835,7 @@
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C393" t="inlineStr">
@@ -20887,7 +20887,7 @@
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
@@ -20939,7 +20939,7 @@
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
@@ -20991,7 +20991,7 @@
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
@@ -21043,7 +21043,7 @@
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C397" t="inlineStr">
@@ -21095,7 +21095,7 @@
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C398" t="inlineStr">
@@ -21147,7 +21147,7 @@
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C399" t="inlineStr">
@@ -21199,7 +21199,7 @@
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C400" t="inlineStr">
@@ -21251,7 +21251,7 @@
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
@@ -21303,7 +21303,7 @@
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
@@ -21355,7 +21355,7 @@
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
@@ -21407,7 +21407,7 @@
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
@@ -21459,7 +21459,7 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
@@ -21511,7 +21511,7 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
@@ -21563,7 +21563,7 @@
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C407" t="inlineStr">
@@ -21615,7 +21615,7 @@
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C408" t="inlineStr">
@@ -21667,7 +21667,7 @@
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C409" t="inlineStr">
@@ -21719,7 +21719,7 @@
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C410" t="inlineStr">
@@ -21771,7 +21771,7 @@
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C411" t="inlineStr">
@@ -21823,7 +21823,7 @@
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C412" t="inlineStr">
@@ -21875,7 +21875,7 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
@@ -21927,7 +21927,7 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
@@ -21979,7 +21979,7 @@
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
@@ -22031,7 +22031,7 @@
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
@@ -22083,7 +22083,7 @@
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C417" t="inlineStr">
@@ -22135,7 +22135,7 @@
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C418" t="inlineStr">
@@ -22187,7 +22187,7 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
@@ -22239,7 +22239,7 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
@@ -22291,7 +22291,7 @@
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C421" t="inlineStr">
@@ -22343,7 +22343,7 @@
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C422" t="inlineStr">
@@ -22395,7 +22395,7 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
@@ -22447,7 +22447,7 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
@@ -22499,7 +22499,7 @@
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
@@ -22551,7 +22551,7 @@
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
@@ -22603,7 +22603,7 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
@@ -22655,7 +22655,7 @@
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C428" t="inlineStr">
@@ -22707,7 +22707,7 @@
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C429" t="inlineStr">
@@ -22759,7 +22759,7 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
@@ -22811,7 +22811,7 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
@@ -22863,7 +22863,7 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
@@ -22915,7 +22915,7 @@
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
@@ -22967,7 +22967,7 @@
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
@@ -23019,7 +23019,7 @@
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
@@ -23071,7 +23071,7 @@
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
@@ -23123,7 +23123,7 @@
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
@@ -23175,7 +23175,7 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
@@ -23227,7 +23227,7 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
@@ -23279,7 +23279,7 @@
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
@@ -23331,7 +23331,7 @@
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
@@ -23383,7 +23383,7 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
@@ -23435,7 +23435,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
@@ -23487,7 +23487,7 @@
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
@@ -23539,7 +23539,7 @@
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
@@ -23591,7 +23591,7 @@
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
@@ -23695,7 +23695,7 @@
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C448" t="inlineStr">
@@ -23747,7 +23747,7 @@
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
@@ -23799,7 +23799,7 @@
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
@@ -23851,7 +23851,7 @@
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C451" t="inlineStr">
@@ -23903,7 +23903,7 @@
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
@@ -23955,7 +23955,7 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
@@ -24007,7 +24007,7 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
@@ -24059,7 +24059,7 @@
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
@@ -24163,7 +24163,7 @@
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
@@ -24215,7 +24215,7 @@
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C458" t="inlineStr">
@@ -24267,7 +24267,7 @@
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C459" t="inlineStr">
@@ -24319,7 +24319,7 @@
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C460" t="inlineStr">
@@ -24371,7 +24371,7 @@
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C461" t="inlineStr">
@@ -24423,7 +24423,7 @@
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
@@ -24475,7 +24475,7 @@
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
@@ -24527,7 +24527,7 @@
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
@@ -24579,7 +24579,7 @@
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C465" t="inlineStr">
@@ -24631,7 +24631,7 @@
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C466" t="inlineStr">
@@ -24683,7 +24683,7 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
@@ -24735,7 +24735,7 @@
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
@@ -24839,7 +24839,7 @@
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
@@ -24891,7 +24891,7 @@
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C471" t="inlineStr">
@@ -24943,7 +24943,7 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
@@ -24995,7 +24995,7 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
@@ -25047,7 +25047,7 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
@@ -25099,7 +25099,7 @@
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C475" t="inlineStr">
@@ -25151,7 +25151,7 @@
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C476" t="inlineStr">
@@ -25203,7 +25203,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C477" t="inlineStr">
@@ -25255,7 +25255,7 @@
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
@@ -25307,7 +25307,7 @@
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C479" t="inlineStr">
@@ -25359,7 +25359,7 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
@@ -25411,7 +25411,7 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
@@ -25463,7 +25463,7 @@
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
@@ -25515,7 +25515,7 @@
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
@@ -25567,7 +25567,7 @@
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C484" t="inlineStr">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C485" t="inlineStr">
@@ -25671,7 +25671,7 @@
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C486" t="inlineStr">
@@ -25723,7 +25723,7 @@
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C487" t="inlineStr">
@@ -25775,7 +25775,7 @@
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C488" t="inlineStr">
@@ -25827,7 +25827,7 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
@@ -25879,7 +25879,7 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
@@ -25983,7 +25983,7 @@
       </c>
       <c r="B492" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C492" t="inlineStr">
@@ -26035,7 +26035,7 @@
       </c>
       <c r="B493" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C493" t="inlineStr">
@@ -26087,7 +26087,7 @@
       </c>
       <c r="B494" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C494" t="inlineStr">
@@ -26139,7 +26139,7 @@
       </c>
       <c r="B495" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C495" t="inlineStr">
@@ -26191,7 +26191,7 @@
       </c>
       <c r="B496" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C496" t="inlineStr">
@@ -26243,7 +26243,7 @@
       </c>
       <c r="B497" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C497" t="inlineStr">
@@ -26295,7 +26295,7 @@
       </c>
       <c r="B498" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C498" t="inlineStr">
@@ -26347,7 +26347,7 @@
       </c>
       <c r="B499" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C499" t="inlineStr">
@@ -26399,7 +26399,7 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
@@ -26451,7 +26451,7 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
@@ -26503,7 +26503,7 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
@@ -26555,7 +26555,7 @@
       </c>
       <c r="B503" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C503" t="inlineStr">
@@ -26607,7 +26607,7 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
@@ -26659,7 +26659,7 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
@@ -26711,7 +26711,7 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
@@ -26763,7 +26763,7 @@
       </c>
       <c r="B507" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C507" t="inlineStr">
@@ -26815,7 +26815,7 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
@@ -26867,7 +26867,7 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
@@ -26919,7 +26919,7 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
@@ -26971,7 +26971,7 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
@@ -27023,7 +27023,7 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
@@ -27075,7 +27075,7 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
@@ -27127,7 +27127,7 @@
       </c>
       <c r="B514" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C514" t="inlineStr">
@@ -27179,7 +27179,7 @@
       </c>
       <c r="B515" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C515" t="inlineStr">
@@ -27231,7 +27231,7 @@
       </c>
       <c r="B516" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C516" t="inlineStr">
@@ -27283,7 +27283,7 @@
       </c>
       <c r="B517" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C517" t="inlineStr">
@@ -27335,7 +27335,7 @@
       </c>
       <c r="B518" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C518" t="inlineStr">
@@ -27387,7 +27387,7 @@
       </c>
       <c r="B519" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C519" t="inlineStr">
@@ -27439,7 +27439,7 @@
       </c>
       <c r="B520" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C520" t="inlineStr">
@@ -27491,7 +27491,7 @@
       </c>
       <c r="B521" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C521" t="inlineStr">
@@ -27543,7 +27543,7 @@
       </c>
       <c r="B522" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C522" t="inlineStr">
@@ -27595,7 +27595,7 @@
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
@@ -27751,7 +27751,7 @@
       </c>
       <c r="B526" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C526" t="inlineStr">
@@ -27803,7 +27803,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
@@ -27855,7 +27855,7 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
@@ -27907,7 +27907,7 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
@@ -27959,7 +27959,7 @@
       </c>
       <c r="B530" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C530" t="inlineStr">
@@ -28011,7 +28011,7 @@
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
@@ -28063,7 +28063,7 @@
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
@@ -28115,7 +28115,7 @@
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
@@ -28167,7 +28167,7 @@
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
@@ -28219,7 +28219,7 @@
       </c>
       <c r="B535" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C535" t="inlineStr">
@@ -28271,7 +28271,7 @@
       </c>
       <c r="B536" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C536" t="inlineStr">
@@ -28323,7 +28323,7 @@
       </c>
       <c r="B537" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C537" t="inlineStr">
@@ -28375,7 +28375,7 @@
       </c>
       <c r="B538" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C538" t="inlineStr">
@@ -28427,7 +28427,7 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
@@ -28479,7 +28479,7 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
@@ -28531,7 +28531,7 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>MARILYN LIZBETH PAIVA LEDESMA</t>
+          <t>DANIEL ARTURO ALVAREZ CUZCANO</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
